--- a/assets/VER_Custom_Input_Form.xlsx
+++ b/assets/VER_Custom_Input_Form.xlsx
@@ -1,58 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="READ ME FIRST" sheetId="1" r:id="rId1"/>
-    <sheet name="1. Header" sheetId="2" r:id="rId2"/>
-    <sheet name="2. Metrics" sheetId="3" r:id="rId3"/>
-    <sheet name="3. Key Points" sheetId="4" r:id="rId4"/>
-    <sheet name="4. Wins" sheetId="5" r:id="rId5"/>
-    <sheet name="5. Next Steps" sheetId="6" r:id="rId6"/>
-    <sheet name="6. Custom Notes" sheetId="7" r:id="rId7"/>
+    <sheet name="READ ME FIRST" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. Header" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. Key Points" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. Wins" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. Next Steps" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. Custom Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -71,13 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -402,313 +446,620 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>VER CUSTOM MEETING INPUT FORM</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>VER CUSTOM MEETING INPUT FORM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" t="str">
-        <v>INSTRUCTIONS</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INSTRUCTIONS</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Fill in each tab with your meeting data.</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fill in each tab with your meeting data.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>All fields are optional — fill what you have.</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All fields are optional — fill what you have.</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Return this file to VER or paste values into the generator.</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Return this file to VER or paste values into the generator.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Field</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Meeting Title</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Meeting Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VER Q1 FY27 Portfolio Rationalization Review</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Presenter</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Presenter</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Casey Candelaria</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Audience</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Audience</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DET Leadership, Roger Espinoza, Joe Martinez</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Purpose</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/A — Portfolio-Level</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FY / Period</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FY27 Q1</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Metric</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tier 3 Vendors in Scope</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Currently under rationalization review for consolidation or exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Estimated Savings Opportunity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$4.2M</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>If 10 vendors consolidated and 3 exited by Q3 FY27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Contracts Expiring in 12 Months</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3 Tier 1, 4 Tier 3 — all require renewal decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Open Governance Items</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Down from 12 at start of FY27 — resolution rate on track</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Preferred Supplier Utilization</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Up from 79% in FY26 — 5-point improvement from rationalization work</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VER Hub Stakeholder Adoption</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Active users across DET in first 90 days since launch</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Key Point</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Detail</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Key Point</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tier 3 rationalization is the single highest-value FY27 initiative</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Approval needed to begin vendor exit conversations — $4.2M opportunity identified</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Seven contracts expire within 12 months — renewal decisions needed now</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IBM and Cognizant are the highest-value renewals; both require rate reduction mandates</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VER Intelligence Hub is ready for broader org packaging</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Joe has already expressed interest — formal pitch ready for office hours this quarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLA compliance portfolio-wide at 94% — best rate since FY23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CQBR accountability cycle is the primary driver; continue and expand to Tier 2 vendors</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Win</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Impact</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Preferred supplier utilization up 5 points to 84%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Directly attributable to VER rationalization guidance and stakeholder education</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Open governance items reduced from 12 to 5 in one quarter</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CQBR cycle accountability is working — vendors responding to formal tracking</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>#</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Action</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Due</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Approve Tier 3 rationalization target list</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DET Leadership</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Begin IBM renewal pre-negotiation with rate mandate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>VER + Procurement</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Schedule VER Hub packaging presentation for Joe office hours</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Casey Candelaria</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Expand CQBR program to Tier 2 vendors — 8 additional suppliers</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VER Team</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Label</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Notes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Decision Needed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Tier 3 rationalization list requires leadership sign-off before VER can initiate vendor conversations. List is ready — 18 vendors scored on utilization, value, and risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hub Packaging</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Joe already expressed informal interest. Formal packaging would require 6-8 weeks of documentation and security review. ROI case is compelling.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>